--- a/results/Int All Data -0.5/Linea_fi_explain.xlsx
+++ b/results/Int All Data -0.5/Linea_fi_explain.xlsx
@@ -1694,7 +1694,7 @@
         <v>0.01299699373665293</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01951624129115841</v>
+        <v>0.01951627887180503</v>
       </c>
       <c r="I3" t="n">
         <v>0.00806783144261421</v>
@@ -1766,7 +1766,7 @@
         <v>0.003429245326110911</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.000282085467269676</v>
+        <v>0.0002851709347179942</v>
       </c>
       <c r="AG3" t="n">
         <v>-0.0002408617749808872</v>
@@ -1826,13 +1826,13 @@
         <v>0.06741495417114403</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.186527410272033e-05</v>
+        <v>1.889173856897133e-05</v>
       </c>
       <c r="BA3" t="n">
         <v>0.006318213227589719</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.01524861535090282</v>
+        <v>0.01525158888643657</v>
       </c>
       <c r="BC3" t="n">
         <v>8.510309336304806e-05</v>
@@ -1847,7 +1847,7 @@
         <v>-0.001485401247159145</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.0005787523202360612</v>
+        <v>-0.0005819158760728216</v>
       </c>
       <c r="BH3" t="n">
         <v>0.008597376307593611</v>
@@ -1883,7 +1883,7 @@
         <v>0.01816684941143121</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.001955448369638873</v>
+        <v>0.001958611925475634</v>
       </c>
       <c r="BT3" t="n">
         <v>-0.0008869886155053696</v>
@@ -1895,10 +1895,10 @@
         <v>0.0003051594470671503</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.0001166943853790237</v>
+        <v>0.0001197798528273419</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.004584461666323569</v>
+        <v>0.004587454782157152</v>
       </c>
       <c r="BY3" t="n">
         <v>0.001056380233022009</v>
@@ -1913,7 +1913,7 @@
         <v>0.003785081994129477</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.01486732101080753</v>
+        <v>0.0148704845666443</v>
       </c>
       <c r="CD3" t="n">
         <v>0.001860951710623624</v>
@@ -1934,7 +1934,7 @@
         <v>0.2390471470437886</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.0001197798528273419</v>
+        <v>0.0001166943853790237</v>
       </c>
       <c r="CK3" t="n">
         <v>0.0007763841325047516</v>
@@ -2108,7 +2108,7 @@
         <v>-0.0005483145604904838</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.001621152300230251</v>
+        <v>0.001618179648625019</v>
       </c>
       <c r="EQ3" t="n">
         <v>0.008556258305204281</v>
@@ -2163,7 +2163,7 @@
         <v>0.01699669843607382</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02610697011525708</v>
+        <v>0.02610317872908455</v>
       </c>
       <c r="I4" t="n">
         <v>0.01710984504058647</v>
@@ -2235,7 +2235,7 @@
         <v>0.00467903775265742</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.009072129147722112</v>
+        <v>0.009071992816050355</v>
       </c>
       <c r="AG4" t="n">
         <v>0.001077460982843898</v>
@@ -2295,13 +2295,13 @@
         <v>0.03640400022816315</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.00149484196720366</v>
+        <v>0.001494525505583128</v>
       </c>
       <c r="BA4" t="n">
         <v>0.006979605542071663</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.01169707448101166</v>
+        <v>0.01169844880136882</v>
       </c>
       <c r="BC4" t="n">
         <v>0.002329827190410264</v>
@@ -2316,7 +2316,7 @@
         <v>0.004363062284789061</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.006781684848952931</v>
+        <v>0.006784572701319404</v>
       </c>
       <c r="BH4" t="n">
         <v>0.01543665799724937</v>
@@ -2352,7 +2352,7 @@
         <v>0.01712377683578</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.004749918038653633</v>
+        <v>0.004747263370750696</v>
       </c>
       <c r="BT4" t="n">
         <v>0.003339240272744403</v>
@@ -2364,10 +2364,10 @@
         <v>0.01095509488484823</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0006268630763621236</v>
+        <v>0.0006295013846488363</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.01137545911381353</v>
+        <v>0.01137391263802918</v>
       </c>
       <c r="BY4" t="n">
         <v>0.004248815670847278</v>
@@ -2382,7 +2382,7 @@
         <v>0.008959708184002572</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.03247210665288083</v>
+        <v>0.03246739930646286</v>
       </c>
       <c r="CD4" t="n">
         <v>0.01350279319152689</v>
@@ -2403,7 +2403,7 @@
         <v>0.05036802041270115</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0006295013846488363</v>
+        <v>0.0006268630763621236</v>
       </c>
       <c r="CK4" t="n">
         <v>0.004499575167037658</v>
@@ -2577,7 +2577,7 @@
         <v>0.001280589986834559</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.005714652426759182</v>
+        <v>0.005715012974374939</v>
       </c>
       <c r="EQ4" t="n">
         <v>0.03065872329244416</v>
@@ -2632,7 +2632,7 @@
         <v>-0.001095890410958944</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.007620237351655157</v>
+        <v>-0.00758900687070575</v>
       </c>
       <c r="I5" t="n">
         <v>-0.0138269402319358</v>
@@ -2851,7 +2851,7 @@
         <v>-0.008432267884322752</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.02863018032268271</v>
+        <v>-0.02859854476431509</v>
       </c>
       <c r="CD5" t="n">
         <v>-0.03185700727617843</v>
@@ -3254,7 +3254,7 @@
         <v>-0.004291323925371462</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.005420696014267715</v>
+        <v>-0.005444422683043418</v>
       </c>
       <c r="BH6" t="n">
         <v>0.001099858328556802</v>
@@ -3290,7 +3290,7 @@
         <v>0.008283431517127581</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.001330977841333542</v>
+        <v>-0.001314819161736292</v>
       </c>
       <c r="BT6" t="n">
         <v>-0.001766831608922065</v>
@@ -3305,7 +3305,7 @@
         <v>-0.0002824814560636379</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.0002117691734693922</v>
+        <v>-0.0001893208047175216</v>
       </c>
       <c r="BY6" t="n">
         <v>-0.002758359163753871</v>
@@ -3702,7 +3702,7 @@
         <v>0.05219740719737843</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.0001341028035162062</v>
+        <v>0.0001192351258474611</v>
       </c>
       <c r="BA7" t="n">
         <v>0.003292862985838046</v>
@@ -4039,7 +4039,7 @@
         <v>0.01613769290414005</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01985072562048971</v>
+        <v>0.01982758461462732</v>
       </c>
       <c r="I8" t="n">
         <v>0.01288562802367621</v>
@@ -4111,7 +4111,7 @@
         <v>0.003488949329441532</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0009421388504680439</v>
+        <v>0.0009498525190888396</v>
       </c>
       <c r="AG8" t="n">
         <v>0.0003585032427684626</v>
@@ -4177,7 +4177,7 @@
         <v>0.01365251897091525</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.01923590108145069</v>
+        <v>0.0192582025979538</v>
       </c>
       <c r="BC8" t="n">
         <v>0.0001291208303094121</v>
@@ -4240,7 +4240,7 @@
         <v>0.002948026590899039</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.0005137751398382379</v>
+        <v>0.0005369161457006249</v>
       </c>
       <c r="BX8" t="n">
         <v>0.009821870315560696</v>
@@ -4279,7 +4279,7 @@
         <v>0.2533569021650763</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.0005369161457006249</v>
+        <v>0.0005137751398382379</v>
       </c>
       <c r="CK8" t="n">
         <v>0.005168215982418936</v>
